--- a/output/reports/车辆路径优化汇总报告.xlsx
+++ b/output/reports/车辆路径优化汇总报告.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="车辆汇总" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="详细路径" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="统计分析" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="车辆汇总" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详细路径" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="统计分析" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1061,28 +1061,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LTL货车</t>
+          <t>9.6米厢式货车</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>失败</t>
+          <t>成功</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>96.14</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>131.16</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1094,22 +1094,30 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>无解</t>
+          <t>Nearest_Neighbor_TSP</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>无有效路径解</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
+          <t>MULTI_STOP_OPTIMIZED</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="11">
@@ -1120,7 +1128,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>9.6米箱式货车</t>
+          <t>9.6米厢式货车</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1129,40 +1137,40 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>141.69</v>
+        <v>160.21</v>
       </c>
       <c r="E11" t="n">
-        <v>3.54</v>
+        <v>5.51</v>
       </c>
       <c r="F11" t="n">
-        <v>214.49</v>
+        <v>218.44</v>
       </c>
       <c r="G11" t="n">
+        <v>4</v>
+      </c>
+      <c r="H11" t="n">
         <v>3</v>
       </c>
-      <c r="H11" t="n">
-        <v>2</v>
-      </c>
       <c r="I11" t="n">
         <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>1922</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>7834</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>12.81</v>
+        <v>0.28</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Heuristic_NearestNeighbor</t>
+          <t>Nearest_Neighbor_TSP</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>HEURISTIC_FEASIBLE</t>
+          <t>MULTI_STOP_OPTIMIZED</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1172,11 +1180,11 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>3.54</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="12">
@@ -1187,7 +1195,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>9.6米箱式货车</t>
+          <t>9.6米厢式货车</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1196,40 +1204,40 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>115.44</v>
+        <v>129.83</v>
       </c>
       <c r="E12" t="n">
-        <v>2.89</v>
+        <v>5.41</v>
       </c>
       <c r="F12" t="n">
-        <v>174.75</v>
+        <v>177.67</v>
       </c>
       <c r="G12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>1922</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>10796</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>12.81</v>
+        <v>0.71</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Heuristic_NearestNeighbor</t>
+          <t>Nearest_Neighbor_TSP</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>HEURISTIC_FEASIBLE</t>
+          <t>MULTI_STOP_OPTIMIZED</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1239,11 +1247,11 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>2.89</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="13">
@@ -1254,7 +1262,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>9.6米箱式货车</t>
+          <t>9.6米厢式货车</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1266,10 +1274,10 @@
         <v>99.23</v>
       </c>
       <c r="E13" t="n">
-        <v>2.48</v>
+        <v>3.65</v>
       </c>
       <c r="F13" t="n">
-        <v>207.63</v>
+        <v>135.13</v>
       </c>
       <c r="G13" t="n">
         <v>3</v>
@@ -1281,22 +1289,22 @@
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>9156</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>7378</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>61.04</v>
+        <v>0.15</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Heuristic_NearestNeighbor</t>
+          <t>Nearest_Neighbor_TSP</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>HEURISTIC_FEASIBLE</t>
+          <t>MULTI_STOP_OPTIMIZED</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1306,11 +1314,11 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>2.48</v>
+        <v>3.65</v>
       </c>
     </row>
   </sheetData>
@@ -1324,7 +1332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1821,7 +1829,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LTL_TRUCK_01</t>
+          <t>LTL_TRUCK_00</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1834,47 +1842,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ORDER_0031</t>
+          <t>ORDER_0027</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>30.851558</v>
+        <v>30.867638</v>
       </c>
       <c r="F10" t="n">
-        <v>104.28116</v>
+        <v>104.036469</v>
       </c>
       <c r="G10" t="n">
-        <v>4347</v>
+        <v>18.67</v>
       </c>
       <c r="H10" t="n">
-        <v>6269</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>14.69</v>
+        <v>12.3</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>坐标(30.8516, 104.2812)</t>
+          <t>坐标(30.8676, 104.0365)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LTL_TRUCK_01</t>
+          <t>LTL_TRUCK_00</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1887,47 +1895,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ORDER_0040</t>
+          <t>ORDER_0032</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>30.399125</v>
+        <v>30.784712</v>
       </c>
       <c r="F11" t="n">
-        <v>104.558069</v>
+        <v>104.286461</v>
       </c>
       <c r="G11" t="n">
-        <v>3487</v>
+        <v>10.77</v>
       </c>
       <c r="H11" t="n">
-        <v>9756</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>56.86</v>
+        <v>25.59</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>坐标(30.3991, 104.5581)</t>
+          <t>坐标(30.7847, 104.2865)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LTL_TRUCK_01</t>
+          <t>LTL_TRUCK_00</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1935,52 +1943,52 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>送货</t>
+          <t>取货</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ORDER_0011</t>
+          <t>ORDER_0036</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>30.76405</v>
+        <v>30.539113</v>
       </c>
       <c r="F12" t="n">
-        <v>104.0668</v>
+        <v>104.196005</v>
       </c>
       <c r="G12" t="n">
-        <v>-1922</v>
+        <v>23.72</v>
       </c>
       <c r="H12" t="n">
-        <v>7834</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>62.11</v>
+        <v>28.65</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>坐标(30.7641, 104.0668)</t>
+          <t>坐标(30.5391, 104.1960)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LTL_TRUCK_02</t>
+          <t>LTL_TRUCK_01</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -2003,7 +2011,7 @@
         <v>104.0668</v>
       </c>
       <c r="G13" t="n">
-        <v>-1922</v>
+        <v>-6.2</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -2017,11 +2025,11 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -2033,7 +2041,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LTL_TRUCK_02</t>
+          <t>LTL_TRUCK_01</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2046,47 +2054,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ORDER_0022</t>
+          <t>ORDER_0027</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>30.689311</v>
+        <v>30.867638</v>
       </c>
       <c r="F14" t="n">
-        <v>104.086109</v>
+        <v>104.036469</v>
       </c>
       <c r="G14" t="n">
-        <v>1697</v>
+        <v>18.67</v>
       </c>
       <c r="H14" t="n">
-        <v>1697</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>8.51</v>
+        <v>11.88</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>坐标(30.6893, 104.0861)</t>
+          <t>坐标(30.8676, 104.0365)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LTL_TRUCK_02</t>
+          <t>LTL_TRUCK_01</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -2099,47 +2107,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ORDER_0033</t>
+          <t>ORDER_0031</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>30.737656</v>
+        <v>30.851558</v>
       </c>
       <c r="F15" t="n">
-        <v>104.609837</v>
+        <v>104.28116</v>
       </c>
       <c r="G15" t="n">
-        <v>4752</v>
+        <v>10.35</v>
       </c>
       <c r="H15" t="n">
-        <v>6449</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>50.35</v>
+        <v>23.42</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>坐标(30.7377, 104.6098)</t>
+          <t>坐标(30.8516, 104.2812)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LTL_TRUCK_02</t>
+          <t>LTL_TRUCK_01</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -2152,47 +2160,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ORDER_0031</t>
+          <t>ORDER_0040</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>30.851558</v>
+        <v>30.399125</v>
       </c>
       <c r="F16" t="n">
-        <v>104.28116</v>
+        <v>104.558069</v>
       </c>
       <c r="G16" t="n">
-        <v>4347</v>
+        <v>7.42</v>
       </c>
       <c r="H16" t="n">
-        <v>10796</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>33.85</v>
+        <v>56.86</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>坐标(30.8516, 104.2812)</t>
+          <t>坐标(30.3991, 104.5581)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LTL_TRUCK_03</t>
+          <t>LTL_TRUCK_02</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2200,52 +2208,52 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>送货</t>
+          <t>取货</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ORDER_0012</t>
+          <t>ORDER_0026</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>30.84101</v>
+        <v>30.802111</v>
       </c>
       <c r="F17" t="n">
-        <v>104.1591</v>
+        <v>104.164075</v>
       </c>
       <c r="G17" t="n">
-        <v>-9156</v>
+        <v>68.16</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>4.86</v>
+        <v>2.39</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>坐标(30.8410, 104.1591)</t>
+          <t>坐标(30.8021, 104.1641)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LTL_TRUCK_03</t>
+          <t>LTL_TRUCK_02</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2253,52 +2261,52 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>取货</t>
+          <t>送货</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ORDER_0030</t>
+          <t>ORDER_0011</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>30.893214</v>
+        <v>30.76405</v>
       </c>
       <c r="F18" t="n">
-        <v>104.269026</v>
+        <v>104.0668</v>
       </c>
       <c r="G18" t="n">
-        <v>2626</v>
+        <v>-6.2</v>
       </c>
       <c r="H18" t="n">
-        <v>2626</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>11.99</v>
+        <v>10.21</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>坐标(30.8932, 104.2690)</t>
+          <t>坐标(30.7641, 104.0668)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LTL_TRUCK_03</t>
+          <t>LTL_TRUCK_02</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2311,38 +2319,356 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>ORDER_0022</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>30.689311</v>
+      </c>
+      <c r="F19" t="n">
+        <v>104.086109</v>
+      </c>
+      <c r="G19" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>8.51</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>20</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>坐标(30.6893, 104.0861)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>LTL_TRUCK_02</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>4</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>取货</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ORDER_0032</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>30.784712</v>
+      </c>
+      <c r="F20" t="n">
+        <v>104.286461</v>
+      </c>
+      <c r="G20" t="n">
+        <v>10.77</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>21.89</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>20</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>坐标(30.7847, 104.2865)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>LTL_TRUCK_02</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>取货</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ORDER_0031</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>30.851558</v>
+      </c>
+      <c r="F21" t="n">
+        <v>104.28116</v>
+      </c>
+      <c r="G21" t="n">
+        <v>10.35</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>20</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>坐标(30.8516, 104.2812)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>LTL_TRUCK_02</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>6</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>取货</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
           <t>ORDER_0033</t>
         </is>
       </c>
-      <c r="E19" t="n">
+      <c r="E22" t="n">
         <v>30.737656</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F22" t="n">
         <v>104.609837</v>
       </c>
-      <c r="G19" t="n">
-        <v>4752</v>
-      </c>
-      <c r="H19" t="n">
-        <v>7378</v>
-      </c>
-      <c r="I19" t="n">
+      <c r="G22" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>33.85</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>20</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>坐标(30.7377, 104.6098)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>LTL_TRUCK_03</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>送货</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ORDER_0012</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>30.84101</v>
+      </c>
+      <c r="F23" t="n">
+        <v>104.1591</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-12</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>08:07</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>30</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>08:37</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>坐标(30.8410, 104.1591)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>LTL_TRUCK_03</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>取货</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ORDER_0030</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>30.893214</v>
+      </c>
+      <c r="F24" t="n">
+        <v>104.269026</v>
+      </c>
+      <c r="G24" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>20</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>坐标(30.8932, 104.2690)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>LTL_TRUCK_03</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>3</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>取货</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ORDER_0033</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>30.737656</v>
+      </c>
+      <c r="F25" t="n">
+        <v>104.609837</v>
+      </c>
+      <c r="G25" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
         <v>36.86</v>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>10</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>09:55</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>20</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
         <is>
           <t>坐标(30.7377, 104.6098)</t>
         </is>
@@ -2359,7 +2685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2391,7 +2717,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -2401,7 +2727,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2411,7 +2737,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>91.67</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6">
@@ -2432,7 +2758,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>515.98</v>
+        <v>645.0300000000001</v>
       </c>
     </row>
     <row r="9">
@@ -2442,7 +2768,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>46.91</v>
+        <v>53.75</v>
       </c>
     </row>
     <row r="10">
@@ -2452,7 +2778,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2063.2</v>
+        <v>2128.73</v>
       </c>
     </row>
     <row r="11">
@@ -2462,7 +2788,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>187.56</v>
+        <v>177.39</v>
       </c>
     </row>
     <row r="12">
@@ -2472,7 +2798,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13">
@@ -2482,7 +2808,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.64</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -2492,7 +2818,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15.55</v>
+        <v>24.61</v>
       </c>
     </row>
     <row r="15">
@@ -2502,38 +2828,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.41</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17">
-        <f>== 失败车辆分析 ===</f>
-        <v/>
-      </c>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>大型货车失败数</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>LTL货车失败数</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
+        <v>2.05</v>
       </c>
     </row>
   </sheetData>

--- a/output/reports/车辆路径优化汇总报告.xlsx
+++ b/output/reports/车辆路径优化汇总报告.xlsx
@@ -1070,19 +1070,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>96.14</v>
+        <v>72.44</v>
       </c>
       <c r="E10" t="n">
-        <v>3.4</v>
+        <v>2.48</v>
       </c>
       <c r="F10" t="n">
-        <v>131.16</v>
+        <v>98.72</v>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1094,7 +1094,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.35</v>
+        <v>0.23</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1113,11 +1113,11 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>3.4</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="11">
@@ -1137,22 +1137,22 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>160.21</v>
+        <v>149.94</v>
       </c>
       <c r="E11" t="n">
-        <v>5.51</v>
+        <v>4.75</v>
       </c>
       <c r="F11" t="n">
-        <v>218.44</v>
+        <v>204.52</v>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
         <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1161,7 +1161,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0.28</v>
+        <v>0.33</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1180,11 +1180,11 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>5.51</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="12">
@@ -1204,22 +1204,22 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>129.83</v>
+        <v>169.2</v>
       </c>
       <c r="E12" t="n">
-        <v>5.41</v>
+        <v>6.56</v>
       </c>
       <c r="F12" t="n">
-        <v>177.67</v>
+        <v>230.82</v>
       </c>
       <c r="G12" t="n">
         <v>6</v>
       </c>
       <c r="H12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0.71</v>
+        <v>0.35</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1247,11 +1247,11 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>5.41</v>
+        <v>6.56</v>
       </c>
     </row>
     <row r="13">
@@ -1271,19 +1271,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>99.23</v>
+        <v>143.23</v>
       </c>
       <c r="E13" t="n">
-        <v>3.65</v>
+        <v>5.41</v>
       </c>
       <c r="F13" t="n">
-        <v>135.13</v>
+        <v>195.9</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
@@ -1295,7 +1295,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0.15</v>
+        <v>0.64</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1314,11 +1314,11 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>3.65</v>
+        <v>5.41</v>
       </c>
     </row>
   </sheetData>
@@ -1842,27 +1842,27 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ORDER_0027</t>
+          <t>ORDER_0032</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>30.867638</v>
+        <v>30.784712</v>
       </c>
       <c r="F10" t="n">
-        <v>104.036469</v>
+        <v>104.286461</v>
       </c>
       <c r="G10" t="n">
-        <v>18.67</v>
+        <v>10.77</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>12.3</v>
+        <v>14.19</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1870,12 +1870,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>坐标(30.8676, 104.0365)</t>
+          <t>坐标(30.7847, 104.2865)</t>
         </is>
       </c>
     </row>
@@ -1895,27 +1895,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ORDER_0032</t>
+          <t>ORDER_0036</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>30.784712</v>
+        <v>30.539113</v>
       </c>
       <c r="F11" t="n">
-        <v>104.286461</v>
+        <v>104.196005</v>
       </c>
       <c r="G11" t="n">
-        <v>10.77</v>
+        <v>23.72</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>25.59</v>
+        <v>28.65</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1923,23 +1923,23 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>坐标(30.7847, 104.2865)</t>
+          <t>坐标(30.5391, 104.1960)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LTL_TRUCK_00</t>
+          <t>LTL_TRUCK_01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1948,27 +1948,27 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ORDER_0036</t>
+          <t>ORDER_0027</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>30.539113</v>
+        <v>30.867638</v>
       </c>
       <c r="F12" t="n">
-        <v>104.196005</v>
+        <v>104.036469</v>
       </c>
       <c r="G12" t="n">
-        <v>23.72</v>
+        <v>18.67</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>28.65</v>
+        <v>12.3</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1976,12 +1976,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>坐标(30.5391, 104.1960)</t>
+          <t>坐标(30.8676, 104.0365)</t>
         </is>
       </c>
     </row>
@@ -1992,49 +1992,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>送货</t>
+          <t>取货</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ORDER_0011</t>
+          <t>ORDER_0036</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>30.76405</v>
+        <v>30.539113</v>
       </c>
       <c r="F13" t="n">
-        <v>104.0668</v>
+        <v>104.196005</v>
       </c>
       <c r="G13" t="n">
-        <v>-6.2</v>
+        <v>23.72</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>8.029999999999999</v>
+        <v>39.59</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>坐标(30.7641, 104.0668)</t>
+          <t>坐标(30.5391, 104.1960)</t>
         </is>
       </c>
     </row>
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2054,27 +2054,27 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ORDER_0027</t>
+          <t>ORDER_0040</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>30.867638</v>
+        <v>30.399125</v>
       </c>
       <c r="F14" t="n">
-        <v>104.036469</v>
+        <v>104.558069</v>
       </c>
       <c r="G14" t="n">
-        <v>18.67</v>
+        <v>7.42</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>11.88</v>
+        <v>38.03</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -2082,76 +2082,76 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>坐标(30.8676, 104.0365)</t>
+          <t>坐标(30.3991, 104.5581)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LTL_TRUCK_01</t>
+          <t>LTL_TRUCK_02</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>取货</t>
+          <t>送货</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ORDER_0031</t>
+          <t>ORDER_0012</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>30.851558</v>
+        <v>30.84101</v>
       </c>
       <c r="F15" t="n">
-        <v>104.28116</v>
+        <v>104.1591</v>
       </c>
       <c r="G15" t="n">
-        <v>10.35</v>
+        <v>-12</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>23.42</v>
+        <v>4.86</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>坐标(30.8516, 104.2812)</t>
+          <t>坐标(30.8410, 104.1591)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LTL_TRUCK_01</t>
+          <t>LTL_TRUCK_02</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2160,27 +2160,27 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ORDER_0040</t>
+          <t>ORDER_0031</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>30.399125</v>
+        <v>30.851558</v>
       </c>
       <c r="F16" t="n">
-        <v>104.558069</v>
+        <v>104.28116</v>
       </c>
       <c r="G16" t="n">
-        <v>7.42</v>
+        <v>10.35</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>56.86</v>
+        <v>11.71</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>坐标(30.3991, 104.5581)</t>
+          <t>坐标(30.8516, 104.2812)</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2213,27 +2213,27 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ORDER_0026</t>
+          <t>ORDER_0032</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>30.802111</v>
+        <v>30.784712</v>
       </c>
       <c r="F17" t="n">
-        <v>104.164075</v>
+        <v>104.286461</v>
       </c>
       <c r="G17" t="n">
-        <v>68.16</v>
+        <v>10.77</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>2.39</v>
+        <v>7.45</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -2241,12 +2241,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>坐标(30.8021, 104.1641)</t>
+          <t>坐标(30.7847, 104.2865)</t>
         </is>
       </c>
     </row>
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2282,11 +2282,11 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>10.21</v>
+        <v>21.11</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2310,7 +2310,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2363,7 +2363,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2372,27 +2372,27 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ORDER_0032</t>
+          <t>ORDER_0040</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>30.784712</v>
+        <v>30.399125</v>
       </c>
       <c r="F20" t="n">
-        <v>104.286461</v>
+        <v>104.558069</v>
       </c>
       <c r="G20" t="n">
-        <v>10.77</v>
+        <v>7.42</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>21.89</v>
+        <v>55.53</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -2400,23 +2400,23 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>坐标(30.7847, 104.2865)</t>
+          <t>坐标(30.3991, 104.5581)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LTL_TRUCK_02</t>
+          <t>LTL_TRUCK_03</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2425,27 +2425,27 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ORDER_0031</t>
+          <t>ORDER_0026</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>30.851558</v>
+        <v>30.802111</v>
       </c>
       <c r="F21" t="n">
-        <v>104.28116</v>
+        <v>104.164075</v>
       </c>
       <c r="G21" t="n">
-        <v>10.35</v>
+        <v>68.16</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>7.45</v>
+        <v>2.39</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -2453,65 +2453,65 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>坐标(30.8516, 104.2812)</t>
+          <t>坐标(30.8021, 104.1641)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LTL_TRUCK_02</t>
+          <t>LTL_TRUCK_03</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>取货</t>
+          <t>送货</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ORDER_0033</t>
+          <t>ORDER_0012</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>30.737656</v>
+        <v>30.84101</v>
       </c>
       <c r="F22" t="n">
-        <v>104.609837</v>
+        <v>104.1591</v>
       </c>
       <c r="G22" t="n">
-        <v>5.97</v>
+        <v>-12</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>33.85</v>
+        <v>4.35</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>坐标(30.7377, 104.6098)</t>
+          <t>坐标(30.8410, 104.1591)</t>
         </is>
       </c>
     </row>
@@ -2522,49 +2522,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>送货</t>
+          <t>取货</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ORDER_0012</t>
+          <t>ORDER_0030</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>30.84101</v>
+        <v>30.893214</v>
       </c>
       <c r="F23" t="n">
-        <v>104.1591</v>
+        <v>104.269026</v>
       </c>
       <c r="G23" t="n">
-        <v>-12</v>
+        <v>5.03</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>4.86</v>
+        <v>11.99</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>坐标(30.8410, 104.1591)</t>
+          <t>坐标(30.8932, 104.2690)</t>
         </is>
       </c>
     </row>
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2584,27 +2584,27 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ORDER_0030</t>
+          <t>ORDER_0022</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>30.893214</v>
+        <v>30.689311</v>
       </c>
       <c r="F24" t="n">
-        <v>104.269026</v>
+        <v>104.086109</v>
       </c>
       <c r="G24" t="n">
-        <v>5.03</v>
+        <v>5.27</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>11.99</v>
+        <v>28.62</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -2612,12 +2612,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>坐标(30.8932, 104.2690)</t>
+          <t>坐标(30.6893, 104.0861)</t>
         </is>
       </c>
     </row>
@@ -2628,7 +2628,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -2653,11 +2653,11 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>36.86</v>
+        <v>50.35</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2758,7 +2758,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>645.0300000000001</v>
+        <v>694.4300000000001</v>
       </c>
     </row>
     <row r="9">
@@ -2768,7 +2768,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>53.75</v>
+        <v>57.87</v>
       </c>
     </row>
     <row r="10">
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2128.73</v>
+        <v>2196.29</v>
       </c>
     </row>
     <row r="11">
@@ -2788,7 +2788,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>177.39</v>
+        <v>183.02</v>
       </c>
     </row>
     <row r="12">
@@ -2818,7 +2818,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>24.61</v>
+        <v>25.84</v>
       </c>
     </row>
     <row r="15">
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
     </row>
   </sheetData>
